--- a/V5.0_双人执行工作区/B_AI交付/02_25问基准与判分/02_25问基准框架_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/02_25问基准与判分/02_25问基准框架_V50.xlsx
@@ -530,12 +530,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>交集暂定2国(TUR/ETH)，口径待冻结对齐</t>
+          <t>交集2国(TUR/ETH)：TUR ODI 31.0亿(2024)/fx12m +22.0%(2025-12)；ETH ODI 20.4亿(2024)/fx12m +23.1%(2025-12)。高汇率风险3国=ETH/TUR/ZWE，ZWE因ODI低于中位数15.28亿未入交集</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>经A01正式表重核一致；ODI高位口径(≥40国中位数)待A04指标字典终对齐，方法不变</t>
         </is>
       </c>
     </row>
@@ -582,7 +587,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>8/24源表重核一致</t>
         </is>
       </c>
     </row>
@@ -629,7 +639,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>8/24重核：23条=Africa9/Asia9/LatinAmerica5，与第一批一致</t>
         </is>
       </c>
     </row>
@@ -671,12 +686,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>随测试国出数，见MVP复算CSV</t>
+          <t>40国逐指标最新值与各自日期已定稿；测试时按选中ISO3从MVP_country_latest出数（B复算与A01正式表全对拍，最大差2.13e-14）</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>储备缺失5国(AGO/BEN/CIV/ETH/IRN)须显示空，不显示0</t>
         </is>
       </c>
     </row>
@@ -718,12 +738,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>空集：40国FX/CPI全≥80%(FX最低166,CPI最低158)</t>
+          <t>空集：40国FX/CPI全≥80%（FX最低166/192、CPI最低158/192）</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>8/24重核一致；is_imputed全False，无插值行</t>
         </is>
       </c>
     </row>
@@ -770,7 +795,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>T3复核覆盖：三收入字段非空合计0</t>
         </is>
       </c>
     </row>
@@ -817,7 +847,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>T3复核覆盖：bridge 8行全region、iso3全空</t>
         </is>
       </c>
     </row>
@@ -1000,12 +1035,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>短债胜8080窗(35.3%)，阈值待冻结</t>
+          <t>美元短债优于黄金=8,080窗(35.3%)；集合=AI1112 CSV中gold_minus_tbill&lt;0的8,080行</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>8/24回归一致；'明显优于'判定阈值待A04冻结，到位后直接筛CSV出集合，无需重算</t>
         </is>
       </c>
     </row>
@@ -1047,12 +1087,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>黄金胜14840窗(64.7%)，与11同表</t>
+          <t>黄金优于美元短债=14,840窗(64.7%)；黄金胜率按期限：90d 60.8%/1y 59.4%/5y 63.6%/10y 90.3%</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>8/24回归一致；与AI-11同表对称</t>
         </is>
       </c>
     </row>
@@ -1141,12 +1186,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>三策略共同键23080零缺失；去金-0.00755/去美元-0.46231</t>
+          <t>三策略共同键23,080零缺失；去黄金-完整=-0.00755；去美元-完整=-0.46231；黄金拖累窗口34.8%、美元拖累16.4%</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>8/24回归一致</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1238,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>等A01辅助表MVP_cycle_state</t>
+          <t>660月主状态分布：通胀过热181/资产泡沫破裂142/衰退71/激进紧缩66/信用系统性37/再通胀2/滞胀1/空160；触发月数：通胀过热250/资产破裂147/衰退103/紧缩100/再通胀77/滞胀38/信用37/通缩6/正常扩张0。注意：scenario内嵌cycle五分类（'正常扩张'含无状态月）与正式primary_state口径不同，答题必须区分两套标签</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>A01已交付，基准定稿；按周期分组差值引用AI-24</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1384,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>待核转人工=40行机提待核</t>
+          <t>待核转人工集合=40行（机提待核-生效日待人工确认）；no_conflict 2,704行</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>8/24重核一致</t>
         </is>
       </c>
     </row>
@@ -1470,12 +1530,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>等A01辅助表</t>
+          <t>最新月2025-12主状态=空（证据不足，非任何状态）：触发器6个未触发+信用系统性/衰退/再通胀证据不足，missing_reason完整；最近有状态月=2025-09 inflation_overheating</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>A01已交付，基准定稿；答'当前处于某状态'即错，必须如实答证据不足并给最近有状态月</t>
         </is>
       </c>
     </row>
@@ -1522,7 +1587,12 @@
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>T3复核覆盖：18条start_date=1970-01-01、review_status全pending、comparability_grade全空</t>
         </is>
       </c>
     </row>
@@ -1564,12 +1634,17 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>拒答：HIST018同上</t>
+          <t>拒答：HIST018同上；comparability_limit为唯一可用边界文本</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>T3复核覆盖</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1686,17 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>五周期分组差值已算(见CSV)</t>
+          <t>五周期分组差值（去黄金/去美元均差）：正常扩张15000:-0.00627/-0.38159；激进紧缩3280:-0.00945/-0.65869；衰退或通缩2080:-0.01763/-0.77195；资产泡沫破裂480:-0.00484/-0.44147；通胀过热2240:-0.00454/-0.43224；黄金拖累占比41.2/23.8/7.9/40.8/32.0%</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>8/24回归一致</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1738,17 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>拒答：只用HIST001两字段(原文已录)</t>
+          <t>拒答：只用HIST001两字段（modern_backtest_allowed=0；comparability_limit原文已录）</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>2026-08-22</t>
+          <t>2026-08-24</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>T3复核覆盖：HIST001/002/018均modern_backtest_allowed=0</t>
         </is>
       </c>
     </row>

--- a/V5.0_双人执行工作区/B_AI交付/02_25问基准与判分/02_25问基准框架_V50.xlsx
+++ b/V5.0_双人执行工作区/B_AI交付/02_25问基准与判分/02_25问基准框架_V50.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25问基准框架" sheetId="1" r:id="R4c65f0ac98134963"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="25问基准框架" sheetId="1" r:id="R9ad82178b5ad4750"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -1236,25 +1236,22 @@
           <x:t xml:space="preserve">按source_id逐字段核对原行</x:t>
         </x:is>
       </x:c>
-      <x:c r="F18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">追溯字段完整率100%；source_id唯一；日期和哈希完全一致</x:t>
-        </x:is>
+      <x:c r="F18" t="str">
+        <x:v>source_id唯一且命中原行；非空字段逐项一致；publication_date、earliest_backtest_date等源表空值须保持空并明确列为缺口；不得补写或推断</x:v>
       </x:c>
       <x:c r="G18" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">无编造来源</x:t>
         </x:is>
       </x:c>
-      <x:c r="H18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">source_id唯一；选中行须10字段100%</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I18" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">2026-08-22</x:t>
-        </x:is>
+      <x:c r="H18" t="str">
+        <x:v>SRC0721唯一行；publication_date、earliest_backtest_date为空属已登记缺口；其余字段按源表核对，空值不计为错误但必须显式披露</x:v>
+      </x:c>
+      <x:c r="I18" t="str">
+        <x:v>2026-09-01</x:v>
+      </x:c>
+      <x:c r="J18" t="str">
+        <x:v>A复核修订：撤销“10字段100%完整”旧口径；缺失保持空且不得编造，交B沿用原问句复测</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
